--- a/Multicancer detection/00_Data/Test.xlsx
+++ b/Multicancer detection/00_Data/Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30106"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSoft\Pycharm\PythonProject\PythonProject\Data analysis\ML\A_Code for manuscript\Source code for submission\Multicancer detection\03_Ensemble\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSoft\Pycharm\PythonProject\PythonProject\Archive\01_tri_cancer_screening\Source code for submission\Multicancer detection\00_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59EE7B0-21B2-4BF2-8740-BDF2FC65C442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3803BC4-EA7D-4360-9D75-69C4E13DA959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30600" yWindow="8004" windowWidth="17400" windowHeight="15036" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -72,27 +72,27 @@
   </si>
   <si>
     <t>dwl(9,1)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(8,3)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(7,5)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(7,3)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(6,5)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dwl(6,4)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -102,19 +102,13 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -124,9 +118,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -137,28 +143,10 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -167,37 +155,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -476,2276 +449,2296 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{ECB82D54-463F-4E3F-8E75-21083A954963}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;1fcce6e1-f179-43c0-8f4e-f27bb1cc8c55&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultColWidth="15.44140625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="15.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="5" width="16.21875" style="2" customWidth="1"/>
-    <col min="6" max="7" width="16.21875" style="11" customWidth="1"/>
-    <col min="8" max="12" width="16.21875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" style="2"/>
-    <col min="14" max="14" width="15.44140625" style="1"/>
-    <col min="15" max="16384" width="15.44140625" style="2"/>
+    <col min="1" max="12" width="16.21875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" style="3"/>
+    <col min="14" max="14" width="15.44140625" style="2"/>
+    <col min="15" max="16384" width="15.44140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:13" s="2" customFormat="1">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <v>-1.29155</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>0.98150999999999999</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <v>-1.89124</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>-0.66444000000000003</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="5">
         <v>0.21515999999999999</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <v>-0.92266999999999999</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="5">
         <v>-1.1593500000000001</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <v>5.8650000000000001E-2</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="5">
         <v>0.71967999999999999</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="5">
         <v>0.89078000000000002</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="5">
         <v>1.7526E-4</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="5">
         <v>-0.31463000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:13" s="2" customFormat="1">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>-0.53503999999999996</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>2.0328300000000001</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>-0.34717999999999999</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>-0.24371999999999999</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="5">
         <v>0.92523</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>1.2905800000000001</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="5">
         <v>-0.84769000000000005</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="5">
         <v>-1.07372</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="5">
         <v>0.98529</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="5">
         <v>1.2314400000000001</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="5">
         <v>-0.37452999999999997</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="5">
         <v>-0.13977999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:13" s="2" customFormat="1">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>-0.96221000000000001</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>1.86612</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>-0.57233999999999996</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>-0.23400000000000001</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="5">
         <v>0.70447000000000004</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>0.26550000000000001</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="5">
         <v>-1.72393</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>-0.14463000000000001</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="5">
         <v>0.87963000000000002</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="5">
         <v>2.0537899999999998</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="5">
         <v>-0.30953999999999998</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="5">
         <v>-0.21637000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:13" s="2" customFormat="1">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>-1.13869</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>2.1290200000000001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>0.40705000000000002</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>-0.58879000000000004</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="5">
         <v>-0.32295000000000001</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>-0.18670999999999999</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="5">
         <v>-1.20458</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>-9.9279999999999993E-2</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <v>1.18167</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="5">
         <v>2.0664500000000001</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="5">
         <v>-0.12927</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="5">
         <v>-0.11526</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:13" s="2" customFormat="1">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>-1.88808</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>1.1025400000000001</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>-1.73874</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>-1.07959</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="5">
         <v>-0.40727000000000002</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>-9.5589999999999994E-2</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="5">
         <v>-2.2662</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>-0.25097999999999998</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <v>0.96492999999999995</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="5">
         <v>1.8979600000000001</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="5">
         <v>-6.037E-2</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="5">
         <v>-6.6439999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="1" customFormat="1">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:13" s="2" customFormat="1">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>-0.18210999999999999</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>0.49035000000000001</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>-0.63836000000000004</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>-1.57552</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="5">
         <v>-0.72760000000000002</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="5">
         <v>-0.24276</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="5">
         <v>-1.1511899999999999</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="5">
         <v>8.0990000000000006E-2</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="5">
         <v>0.89742999999999995</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="5">
         <v>2.40185</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="5">
         <v>-0.36294999999999999</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="5">
         <v>-0.13002</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="1" customFormat="1">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:13" s="2" customFormat="1">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>-1.11012</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>2.726</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>-1.0985</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>-0.63561999999999996</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="5">
         <v>0.21146999999999999</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <v>0.48945</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="5">
         <v>-1.4462600000000001</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="5">
         <v>-0.50153999999999999</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="5">
         <v>0.60045999999999999</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="5">
         <v>0.33884999999999998</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="5">
         <v>-0.32202999999999998</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="5">
         <v>-0.18109</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="1" customFormat="1">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:13" s="2" customFormat="1">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>0.47661999999999999</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>1.68143</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>0.5444</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>-1.48811</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="5">
         <v>-0.60809000000000002</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="5">
         <v>-0.32475999999999999</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="5">
         <v>-1.2466699999999999</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="5">
         <v>-0.92251000000000005</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="5">
         <v>0.86700999999999995</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="5">
         <v>1.47014</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="5">
         <v>-6.9139999999999993E-2</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="5">
         <v>-0.13614999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="1" customFormat="1">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:13" s="2" customFormat="1">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>-1.20753</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>1.46051</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>-0.29826999999999998</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>-0.97199000000000002</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="5">
         <v>-0.21127000000000001</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="5">
         <v>-0.50705</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="5">
         <v>-1.2792300000000001</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="5">
         <v>-0.58880999999999994</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="5">
         <v>0.52356999999999998</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="5">
         <v>1.46879</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="5">
         <v>-0.64246000000000003</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="5">
         <v>-0.50732999999999995</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="1" customFormat="1">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:13" s="2" customFormat="1">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>0.84323999999999999</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>1.4460500000000001</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>-0.28567999999999999</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>-1.1256999999999999</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="5">
         <v>-0.18332000000000001</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="5">
         <v>0.54403000000000001</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="5">
         <v>-0.89593</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="5">
         <v>-0.93486000000000002</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="5">
         <v>0.66369</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="5">
         <v>1.96665</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="5">
         <v>-0.17494999999999999</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="5">
         <v>-0.48925999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="1" customFormat="1">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:13" s="2" customFormat="1">
+      <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>-0.90773999999999999</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>0.39102999999999999</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>1.06088</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>-1.0544500000000001</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="5">
         <v>0.33933999999999997</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <v>0.25753999999999999</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="5">
         <v>-1.25258</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <v>-0.23078000000000001</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="5">
         <v>0.46142</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="5">
         <v>2.0540400000000001</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="5">
         <v>-0.42188999999999999</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="5">
         <v>-0.32740999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="1" customFormat="1">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:13" s="2" customFormat="1">
+      <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>0.59957000000000005</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>1.49509</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>-0.89592000000000005</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>-0.94220999999999999</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="5">
         <v>-0.10721</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="5">
         <v>0.24437999999999999</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="5">
         <v>-0.95803000000000005</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="5">
         <v>-0.77137999999999995</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="5">
         <v>0.58774000000000004</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="5">
         <v>2.00414</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="5">
         <v>-0.33506999999999998</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="5">
         <v>-0.48163</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="1" customFormat="1">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:13" s="2" customFormat="1">
+      <c r="A14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>0.47121000000000002</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>0.97960999999999998</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>-9.8629999999999995E-2</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>-0.78298000000000001</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="5">
         <v>0.25822000000000001</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <v>6.6860000000000003E-2</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="5">
         <v>-0.92657999999999996</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <v>-8.5809999999999997E-2</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="5">
         <v>0.44008000000000003</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="5">
         <v>2.3345899999999999</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="5">
         <v>-0.65066999999999997</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="5">
         <v>-0.26323000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="1" customFormat="1">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:13" s="2" customFormat="1">
+      <c r="A15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>-1.4322600000000001</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>1.45261</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>-0.21496000000000001</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>-1.40872</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="5">
         <v>-3.3059999999999999E-2</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="5">
         <v>-0.17607</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="5">
         <v>-1.5352399999999999</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>-0.63139000000000001</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="5">
         <v>0.50317999999999996</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="5">
         <v>1.9152899999999999</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="5">
         <v>-0.66237000000000001</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="5">
         <v>-0.46153</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="1" customFormat="1">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:13" s="2" customFormat="1">
+      <c r="A16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>0.75770999999999999</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>0.73111999999999999</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>1.3599600000000001</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>-1.28732</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="5">
         <v>0.27906999999999998</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <v>-0.31579000000000002</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="5">
         <v>-0.91056999999999999</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>-0.36431000000000002</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="5">
         <v>0.69211</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="5">
         <v>1.5772999999999999</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="5">
         <v>-0.58228999999999997</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="5">
         <v>-0.25362000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="1" customFormat="1">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:13" s="2" customFormat="1">
+      <c r="A17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>-1.0989899999999999</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>0.47110999999999997</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>-0.27445999999999998</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <v>-1.14347</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="5">
         <v>-0.43713000000000002</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="5">
         <v>-0.18445</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="5">
         <v>-0.38374999999999998</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="5">
         <v>-0.11588</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="5">
         <v>0.93415999999999999</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="5">
         <v>2.2782900000000001</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="5">
         <v>-0.22276000000000001</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="5">
         <v>-0.1704</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="1" customFormat="1">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:13" s="2" customFormat="1">
+      <c r="A18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <v>0.35000999999999999</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>0.86870000000000003</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="5">
         <v>-1.2810999999999999</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <v>-0.61</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="5">
         <v>2.5870000000000001E-2</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="5">
         <v>0.24604999999999999</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="5">
         <v>-0.89485999999999999</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="5">
         <v>0.58650999999999998</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="5">
         <v>0.49493999999999999</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="5">
         <v>2.3099799999999999</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L18" s="5">
         <v>-7.4800000000000005E-2</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M18" s="5">
         <v>-0.10015</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="1" customFormat="1">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:13" s="2" customFormat="1">
+      <c r="A19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>-1.1359300000000001</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>1.2631399999999999</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <v>-1.06067</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <v>-0.35343999999999998</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="5">
         <v>0.66785000000000005</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="5">
         <v>0.82333000000000001</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="5">
         <v>-1.10778</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="5">
         <v>0.28684999999999999</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="5">
         <v>0.76724999999999999</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="5">
         <v>0.96355999999999997</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="5">
         <v>-0.58364000000000005</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="5">
         <v>-0.26879999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="1" customFormat="1">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:13" s="2" customFormat="1">
+      <c r="A20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>-1.13063</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>1.3046800000000001</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="5">
         <v>-1.0992599999999999</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="5">
         <v>-0.22735</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="5">
         <v>0.59038000000000002</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="5">
         <v>0.58965999999999996</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="5">
         <v>-1.33385</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="5">
         <v>8.1700000000000002E-3</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="5">
         <v>0.74312</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="5">
         <v>1.4826900000000001</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="5">
         <v>-0.29959999999999998</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="5">
         <v>-0.21112</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="1" customFormat="1">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:13" s="2" customFormat="1">
+      <c r="A21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="5">
         <v>-1.4419</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>-0.69091999999999998</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="5">
         <v>0.83977999999999997</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="5">
         <v>-2.1839400000000002</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="5">
         <v>-1.31118</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="5">
         <v>-1.04915</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="5">
         <v>-0.25669999999999998</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="5">
         <v>-0.26859</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="5">
         <v>0.94030999999999998</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="5">
         <v>2.28973</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L21" s="5">
         <v>-0.18303</v>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="5">
         <v>0.16705999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="1" customFormat="1">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:13" s="2" customFormat="1">
+      <c r="A22" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="5">
         <v>-1.4561299999999999</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>0.64917999999999998</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="5">
         <v>-1.61114</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="5">
         <v>-1.2473700000000001</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="5">
         <v>0.56967999999999996</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="5">
         <v>0.34127000000000002</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="5">
         <v>-1.3644400000000001</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="5">
         <v>0.64188999999999996</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="5">
         <v>0.61197000000000001</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="5">
         <v>1.56335</v>
       </c>
-      <c r="L22" s="7">
+      <c r="L22" s="5">
         <v>-0.26871</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="5">
         <v>-0.15612999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="1" customFormat="1">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:13" s="2" customFormat="1">
+      <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="5">
         <v>2.1588599999999998</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>1.6730799999999999</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="5">
         <v>2.6048200000000001</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="5">
         <v>-1.0597399999999999</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="5">
         <v>-5.2220000000000003E-2</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="5">
         <v>-0.40466000000000002</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="5">
         <v>-0.48393000000000003</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="5">
         <v>-0.80922000000000005</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="5">
         <v>0.76890999999999998</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="5">
         <v>2.1620200000000001</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L23" s="5">
         <v>-0.27335999999999999</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="5">
         <v>-0.40461000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="1" customFormat="1">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:13" s="2" customFormat="1">
+      <c r="A24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="5">
         <v>-0.36379</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="5">
         <v>1.71407</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="5">
         <v>3.6559699999999999</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="5">
         <v>-0.48975999999999997</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="5">
         <v>0.4834</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="5">
         <v>7.8750000000000001E-2</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="5">
         <v>-0.95467000000000002</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="5">
         <v>-0.69850999999999996</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="5">
         <v>1.17134</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="5">
         <v>1.49756</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="5">
         <v>-0.45535999999999999</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M24" s="5">
         <v>-0.29300999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="1" customFormat="1">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:13" s="2" customFormat="1">
+      <c r="A25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="5">
         <v>1.2878499999999999</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="5">
         <v>2.4138299999999999</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="5">
         <v>2.3342000000000001</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="5">
         <v>-1.02528</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="5">
         <v>0.25631999999999999</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="5">
         <v>8.6800000000000002E-2</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="5">
         <v>-0.58352999999999999</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="5">
         <v>-1.02393</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J25" s="5">
         <v>0.77539000000000002</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="5">
         <v>1.63713</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L25" s="5">
         <v>-0.44938</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="5">
         <v>-0.48610999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="1" customFormat="1">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:13" s="2" customFormat="1">
+      <c r="A26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="5">
         <v>-0.56979999999999997</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="5">
         <v>2.4374899999999999</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="5">
         <v>0.94047999999999998</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="5">
         <v>-0.84433000000000002</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="5">
         <v>0.33300999999999997</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="5">
         <v>-0.21743999999999999</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="5">
         <v>-0.67100000000000004</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="5">
         <v>-0.97572000000000003</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="5">
         <v>0.97172999999999998</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="5">
         <v>1.62293</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="5">
         <v>-0.57991000000000004</v>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="5">
         <v>-0.27938000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="1" customFormat="1">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:13" s="2" customFormat="1">
+      <c r="A27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="5">
         <v>-1.2387900000000001</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="5">
         <v>0.56015000000000004</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="5">
         <v>1.0410000000000001E-2</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="5">
         <v>-0.61543999999999999</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="5">
         <v>0.21582999999999999</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="5">
         <v>-0.40648000000000001</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="5">
         <v>-1.4386699999999999</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="5">
         <v>-0.39615</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="5">
         <v>0.47893999999999998</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="5">
         <v>2.0533199999999998</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="5">
         <v>-0.36889</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="5">
         <v>-0.54744000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="1" customFormat="1">
-      <c r="A28" s="6" t="s">
+    <row r="28" spans="1:13" s="2" customFormat="1">
+      <c r="A28" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="5">
         <v>-1.0137799999999999</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="5">
         <v>1.3275699999999999</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="5">
         <v>-1.38245</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="5">
         <v>3.458E-2</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="5">
         <v>0.71040999999999999</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="5">
         <v>0.55791000000000002</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="5">
         <v>-2.0369999999999999</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="5">
         <v>0.20272999999999999</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J28" s="5">
         <v>0.92071999999999998</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="5">
         <v>1.0113000000000001</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L28" s="5">
         <v>-0.64571999999999996</v>
       </c>
-      <c r="M28" s="7">
+      <c r="M28" s="5">
         <v>-0.28066999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="1" customFormat="1">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:13" s="2" customFormat="1">
+      <c r="A29" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="5">
         <v>-5.2560000000000003E-2</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="5">
         <v>1.05281</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="5">
         <v>-1.07881</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="5">
         <v>-0.27578999999999998</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="5">
         <v>0.80169999999999997</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="5">
         <v>0.46977000000000002</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="5">
         <v>-0.98012999999999995</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="5">
         <v>-0.44955000000000001</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J29" s="5">
         <v>0.68093000000000004</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="5">
         <v>0.16939000000000001</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L29" s="5">
         <v>-0.34003</v>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="5">
         <v>-0.26758999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="1" customFormat="1">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:13" s="2" customFormat="1">
+      <c r="A30" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="5">
         <v>1.40574</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="5">
         <v>0.85729</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="5">
         <v>-1.2095400000000001</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="5">
         <v>-0.85506000000000004</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="5">
         <v>-0.63012000000000001</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="5">
         <v>0.17477000000000001</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="5">
         <v>-0.82245999999999997</v>
       </c>
-      <c r="I30" s="7">
+      <c r="I30" s="5">
         <v>-0.13020999999999999</v>
       </c>
-      <c r="J30" s="7">
+      <c r="J30" s="5">
         <v>0.82116999999999996</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="5">
         <v>2.1841300000000001</v>
       </c>
-      <c r="L30" s="7">
+      <c r="L30" s="5">
         <v>-4.1509999999999998E-2</v>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="5">
         <v>5.9659999999999998E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:13" s="1" customFormat="1">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:13" s="2" customFormat="1">
+      <c r="A31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="5">
         <v>-0.97323999999999999</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="5">
         <v>1.12208</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="5">
         <v>-1.0787199999999999</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="5">
         <v>0.11504</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="5">
         <v>0.55623</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="5">
         <v>0.20688999999999999</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="5">
         <v>-1.97664</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I31" s="5">
         <v>-0.19505</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J31" s="5">
         <v>0.71362999999999999</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="5">
         <v>1.54071</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L31" s="5">
         <v>-0.43301000000000001</v>
       </c>
-      <c r="M31" s="7">
+      <c r="M31" s="5">
         <v>-0.24868999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="1" customFormat="1">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:13" s="2" customFormat="1">
+      <c r="A32" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="5">
         <v>-0.87278</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="5">
         <v>0.11248</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="5">
         <v>-1.0829800000000001</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="5">
         <v>-0.68062</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="5">
         <v>5.0862100000000001E-4</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="5">
         <v>4.0320000000000002E-2</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="5">
         <v>-2.0808499999999999</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I32" s="5">
         <v>0.41625000000000001</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J32" s="5">
         <v>0.75278999999999996</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="5">
         <v>2.1621700000000001</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L32" s="5">
         <v>-6.7369999999999999E-2</v>
       </c>
-      <c r="M32" s="7">
+      <c r="M32" s="5">
         <v>4.965E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="1" customFormat="1">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:13" s="2" customFormat="1">
+      <c r="A33" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="5">
         <v>-0.99894000000000005</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="5">
         <v>1.1591100000000001</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="5">
         <v>-0.98848999999999998</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="5">
         <v>-0.85536999999999996</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="5">
         <v>0.35044999999999998</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="5">
         <v>0.55496000000000001</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="5">
         <v>-1.9414</v>
       </c>
-      <c r="I33" s="7">
+      <c r="I33" s="5">
         <v>6.6180000000000003E-2</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J33" s="5">
         <v>0.39507999999999999</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="5">
         <v>0.85089000000000004</v>
       </c>
-      <c r="L33" s="7">
+      <c r="L33" s="5">
         <v>-0.53737000000000001</v>
       </c>
-      <c r="M33" s="7">
+      <c r="M33" s="5">
         <v>2.5080000000000002E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" s="1" customFormat="1">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:13" s="2" customFormat="1">
+      <c r="A34" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="5">
         <v>-1.25485</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="5">
         <v>1.187E-2</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="5">
         <v>-1.11311</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="5">
         <v>-1.04142</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="5">
         <v>0.49515999999999999</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="5">
         <v>-0.29063</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="5">
         <v>-2.2306599999999999</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="5">
         <v>9.3640000000000001E-2</v>
       </c>
-      <c r="J34" s="7">
+      <c r="J34" s="5">
         <v>0.47254000000000002</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="5">
         <v>0.91871999999999998</v>
       </c>
-      <c r="L34" s="7">
+      <c r="L34" s="5">
         <v>-0.40127000000000002</v>
       </c>
-      <c r="M34" s="7">
+      <c r="M34" s="5">
         <v>-0.18174000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="1" customFormat="1">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:13" s="2" customFormat="1">
+      <c r="A35" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="5">
         <v>-1.28546</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="5">
         <v>0.81972999999999996</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="5">
         <v>-0.41587000000000002</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="5">
         <v>-0.93745999999999996</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="5">
         <v>5.9470000000000002E-2</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="5">
         <v>-1.1145499999999999</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="5">
         <v>-1.90646</v>
       </c>
-      <c r="I35" s="7">
+      <c r="I35" s="5">
         <v>-0.44209999999999999</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="5">
         <v>0.66393999999999997</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="5">
         <v>0.73124999999999996</v>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="5">
         <v>-0.28221000000000002</v>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="5">
         <v>-0.47960000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="1" customFormat="1">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:13" s="2" customFormat="1">
+      <c r="A36" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="5">
         <v>-1.22679</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="5">
         <v>0.81966000000000006</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="5">
         <v>-1.6389999999999998E-2</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="5">
         <v>-1.1285799999999999</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="5">
         <v>0.25786999999999999</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="5">
         <v>-0.29432000000000003</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="5">
         <v>-1.9043099999999999</v>
       </c>
-      <c r="I36" s="7">
+      <c r="I36" s="5">
         <v>-0.2571</v>
       </c>
-      <c r="J36" s="7">
+      <c r="J36" s="5">
         <v>0.75709000000000004</v>
       </c>
-      <c r="K36" s="7">
+      <c r="K36" s="5">
         <v>1.4237</v>
       </c>
-      <c r="L36" s="7">
+      <c r="L36" s="5">
         <v>-0.39706999999999998</v>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="5">
         <v>-0.38031999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="1" customFormat="1">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:13" s="2" customFormat="1">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="5">
         <v>1.6039300000000001</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="5">
         <v>0.83323000000000003</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="5">
         <v>2.4037899999999999</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="5">
         <v>-0.94398000000000004</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="5">
         <v>0.14155000000000001</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="5">
         <v>-0.44652999999999998</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="5">
         <v>-0.64600999999999997</v>
       </c>
-      <c r="I37" s="7">
+      <c r="I37" s="5">
         <v>-0.53241000000000005</v>
       </c>
-      <c r="J37" s="7">
+      <c r="J37" s="5">
         <v>0.98826000000000003</v>
       </c>
-      <c r="K37" s="7">
+      <c r="K37" s="5">
         <v>0.55891000000000002</v>
       </c>
-      <c r="L37" s="7">
+      <c r="L37" s="5">
         <v>-0.44247999999999998</v>
       </c>
-      <c r="M37" s="7">
+      <c r="M37" s="5">
         <v>-0.33034999999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="1" customFormat="1">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:13" s="2" customFormat="1">
+      <c r="A38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="5">
         <v>1.02549</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="5">
         <v>0.33611999999999997</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="5">
         <v>0.43409999999999999</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="5">
         <v>-1.2185299999999999</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="5">
         <v>4.181E-2</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="5">
         <v>-0.28732000000000002</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="5">
         <v>-0.56183000000000005</v>
       </c>
-      <c r="I38" s="7">
+      <c r="I38" s="5">
         <v>-0.69660999999999995</v>
       </c>
-      <c r="J38" s="7">
+      <c r="J38" s="5">
         <v>0.84311000000000003</v>
       </c>
-      <c r="K38" s="7">
+      <c r="K38" s="5">
         <v>1.7056500000000001</v>
       </c>
-      <c r="L38" s="7">
+      <c r="L38" s="5">
         <v>-0.32346999999999998</v>
       </c>
-      <c r="M38" s="7">
+      <c r="M38" s="5">
         <v>-0.46799000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="1" customFormat="1">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:13" s="2" customFormat="1">
+      <c r="A39" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="5">
         <v>1.3457300000000001</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="5">
         <v>1.1219300000000001</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="5">
         <v>-3.5029999999999999E-2</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="5">
         <v>-0.82657999999999998</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="5">
         <v>-2.3599999999999999E-2</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="5">
         <v>-0.67230999999999996</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="5">
         <v>-0.98678999999999994</v>
       </c>
-      <c r="I39" s="7">
+      <c r="I39" s="5">
         <v>-0.5958</v>
       </c>
-      <c r="J39" s="7">
+      <c r="J39" s="5">
         <v>0.95006000000000002</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K39" s="5">
         <v>0.98601000000000005</v>
       </c>
-      <c r="L39" s="7">
+      <c r="L39" s="5">
         <v>-0.25083</v>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="5">
         <v>-0.33595000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="1" customFormat="1">
-      <c r="A40" s="6" t="s">
+    <row r="40" spans="1:13" s="2" customFormat="1">
+      <c r="A40" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="5">
         <v>1.53511</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="5">
         <v>0.28384999999999999</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="5">
         <v>-0.79962999999999995</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="5">
         <v>-0.75634000000000001</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="5">
         <v>-0.48818</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="5">
         <v>-0.69954000000000005</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="5">
         <v>-0.89983999999999997</v>
       </c>
-      <c r="I40" s="7">
+      <c r="I40" s="5">
         <v>-5.9110000000000003E-2</v>
       </c>
-      <c r="J40" s="7">
+      <c r="J40" s="5">
         <v>0.39023999999999998</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K40" s="5">
         <v>0.79152999999999996</v>
       </c>
-      <c r="L40" s="7">
+      <c r="L40" s="5">
         <v>-0.31818999999999997</v>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="5">
         <v>-0.50593999999999995</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="1" customFormat="1">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:13" s="2" customFormat="1">
+      <c r="A41" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="5">
         <v>-0.92239000000000004</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="5">
         <v>1.3794900000000001</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="5">
         <v>-0.80149999999999999</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="5">
         <v>5.28E-2</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="5">
         <v>0.63182000000000005</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="5">
         <v>0.25452999999999998</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="5">
         <v>-1.8311200000000001</v>
       </c>
-      <c r="I41" s="7">
+      <c r="I41" s="5">
         <v>-0.42242000000000002</v>
       </c>
-      <c r="J41" s="7">
+      <c r="J41" s="5">
         <v>0.61245000000000005</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K41" s="5">
         <v>1.2560800000000001</v>
       </c>
-      <c r="L41" s="7">
+      <c r="L41" s="5">
         <v>-0.51185000000000003</v>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="5">
         <v>-0.12891</v>
       </c>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="5">
         <v>2.9369299999999998</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="5">
         <v>1.32355</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="5">
         <v>-1.4099900000000001</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="5">
         <v>-0.65783000000000003</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="5">
         <v>8.1790000000000002E-2</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="5">
         <v>-8.1989999999999993E-2</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="5">
         <v>-0.56225000000000003</v>
       </c>
-      <c r="I42" s="7">
+      <c r="I42" s="5">
         <v>-0.27133000000000002</v>
       </c>
-      <c r="J42" s="7">
+      <c r="J42" s="5">
         <v>0.63438000000000005</v>
       </c>
-      <c r="K42" s="7">
+      <c r="K42" s="5">
         <v>2.2447300000000001</v>
       </c>
-      <c r="L42" s="7">
+      <c r="L42" s="5">
         <v>-0.27267999999999998</v>
       </c>
-      <c r="M42" s="7">
+      <c r="M42" s="5">
         <v>0.36362</v>
       </c>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="5">
         <v>1.56942</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="5">
         <v>0.70964000000000005</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="5">
         <v>-1.46147</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="5">
         <v>-0.59494999999999998</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="5">
         <v>-0.16158</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="5">
         <v>-0.28858</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="5">
         <v>-1.0677000000000001</v>
       </c>
-      <c r="I43" s="7">
+      <c r="I43" s="5">
         <v>-0.34122000000000002</v>
       </c>
-      <c r="J43" s="7">
+      <c r="J43" s="5">
         <v>0.42444999999999999</v>
       </c>
-      <c r="K43" s="7">
+      <c r="K43" s="5">
         <v>2.24193</v>
       </c>
-      <c r="L43" s="7">
+      <c r="L43" s="5">
         <v>-0.34732000000000002</v>
       </c>
-      <c r="M43" s="7">
+      <c r="M43" s="5">
         <v>0.10390000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="5">
         <v>-0.88285000000000002</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="5">
         <v>1.42215</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="5">
         <v>-1.4401999999999999</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="5">
         <v>-0.72763999999999995</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="5">
         <v>0.36224000000000001</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="5">
         <v>0.33376</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="5">
         <v>-2.0600299999999998</v>
       </c>
-      <c r="I44" s="7">
+      <c r="I44" s="5">
         <v>-0.43874000000000002</v>
       </c>
-      <c r="J44" s="7">
+      <c r="J44" s="5">
         <v>0.81827000000000005</v>
       </c>
-      <c r="K44" s="7">
+      <c r="K44" s="5">
         <v>2.4324699999999999</v>
       </c>
-      <c r="L44" s="7">
+      <c r="L44" s="5">
         <v>-0.47641</v>
       </c>
-      <c r="M44" s="7">
+      <c r="M44" s="5">
         <v>-3.4410000000000003E-2</v>
       </c>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="5">
         <v>-1.1285400000000001</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="5">
         <v>0.80188999999999999</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="5">
         <v>-0.34087000000000001</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="5">
         <v>-0.45427000000000001</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="5">
         <v>-2.2110000000000001E-2</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="5">
         <v>0.35472999999999999</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="5">
         <v>-1.90063</v>
       </c>
-      <c r="I45" s="7">
+      <c r="I45" s="5">
         <v>0.17709</v>
       </c>
-      <c r="J45" s="7">
+      <c r="J45" s="5">
         <v>0.60316000000000003</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K45" s="5">
         <v>1.8084800000000001</v>
       </c>
-      <c r="L45" s="7">
+      <c r="L45" s="5">
         <v>-6.5180000000000002E-2</v>
       </c>
-      <c r="M45" s="7">
+      <c r="M45" s="5">
         <v>1.8579999999999999E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="1" customFormat="1">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:13" s="2" customFormat="1">
+      <c r="A46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="6">
         <v>-1.8058000000000001</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="6">
         <v>0.85258</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="6">
         <v>0.20258000000000001</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="6">
         <v>-0.89205999999999996</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="6">
         <v>0.57845999999999997</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="6">
         <v>0.51160000000000005</v>
       </c>
-      <c r="H46" s="1">
+      <c r="H46" s="6">
         <v>-1.8330599999999999</v>
       </c>
-      <c r="I46" s="1">
+      <c r="I46" s="6">
         <v>0.56654000000000004</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="6">
         <v>-0.48502000000000001</v>
       </c>
-      <c r="K46" s="1">
+      <c r="K46" s="6">
         <v>1.79833</v>
       </c>
-      <c r="L46" s="1">
+      <c r="L46" s="6">
         <v>-0.16866999999999999</v>
       </c>
-      <c r="M46" s="1">
+      <c r="M46" s="6">
         <v>-0.20585999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="1" customFormat="1">
-      <c r="A47" s="6" t="s">
+    <row r="47" spans="1:13" s="2" customFormat="1">
+      <c r="A47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="6">
         <v>-1.57548</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="6">
         <v>0.99522999999999995</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="6">
         <v>0.24099999999999999</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="6">
         <v>-0.86407999999999996</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="6">
         <v>0.45516000000000001</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="6">
         <v>0.59858999999999996</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H47" s="6">
         <v>-1.4654700000000001</v>
       </c>
-      <c r="I47" s="1">
+      <c r="I47" s="6">
         <v>0.53408999999999995</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="6">
         <v>-0.19642000000000001</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K47" s="6">
         <v>1.76593</v>
       </c>
-      <c r="L47" s="1">
+      <c r="L47" s="6">
         <v>-0.21804000000000001</v>
       </c>
-      <c r="M47" s="1">
+      <c r="M47" s="6">
         <v>-8.0960000000000004E-2</v>
       </c>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="6">
         <v>-1.47156</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="6">
         <v>0.91598999999999997</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="6">
         <v>2.7959999999999999E-2</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="6">
         <v>-1.11768</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="6">
         <v>0.41188999999999998</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="6">
         <v>0.77470000000000006</v>
       </c>
-      <c r="H48" s="1">
+      <c r="H48" s="6">
         <v>-1.3954</v>
       </c>
-      <c r="I48" s="1">
+      <c r="I48" s="6">
         <v>0.55069000000000001</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="6">
         <v>-0.44295000000000001</v>
       </c>
-      <c r="K48" s="1">
+      <c r="K48" s="6">
         <v>1.9323600000000001</v>
       </c>
-      <c r="L48" s="1">
+      <c r="L48" s="6">
         <v>-0.15634999999999999</v>
       </c>
-      <c r="M48" s="1">
+      <c r="M48" s="6">
         <v>-2.4279999999999999E-2</v>
       </c>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="6">
         <v>-1.58558</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="6">
         <v>1.6873100000000001</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="6">
         <v>1.0772299999999999</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="6">
         <v>-0.70340000000000003</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="6">
         <v>0.40988999999999998</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="6">
         <v>0.48648000000000002</v>
       </c>
-      <c r="H49" s="1">
+      <c r="H49" s="6">
         <v>-1.4084700000000001</v>
       </c>
-      <c r="I49" s="1">
+      <c r="I49" s="6">
         <v>0.44081999999999999</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="6">
         <v>-2.1919999999999999E-2</v>
       </c>
-      <c r="K49" s="1">
+      <c r="K49" s="6">
         <v>1.62103</v>
       </c>
-      <c r="L49" s="1">
+      <c r="L49" s="6">
         <v>-0.10857</v>
       </c>
-      <c r="M49" s="1">
+      <c r="M49" s="6">
         <v>-0.13672999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="6">
         <v>-1.2528600000000001</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="6">
         <v>0.93096999999999996</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="6">
         <v>1.19156</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="6">
         <v>-0.72248999999999997</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="6">
         <v>0.68572</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="6">
         <v>1.12134</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H50" s="6">
         <v>-1.3321499999999999</v>
       </c>
-      <c r="I50" s="1">
+      <c r="I50" s="6">
         <v>0.33384000000000003</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="6">
         <v>-0.22733999999999999</v>
       </c>
-      <c r="K50" s="1">
+      <c r="K50" s="6">
         <v>1.71817</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L50" s="6">
         <v>-0.1225</v>
       </c>
-      <c r="M50" s="1">
+      <c r="M50" s="6">
         <v>-5.4960000000000002E-2</v>
       </c>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="6">
         <v>-1.85039</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="6">
         <v>1.02996</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" s="6">
         <v>1.2330000000000001E-2</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="6">
         <v>-0.74944999999999995</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="6">
         <v>0.20754</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="6">
         <v>0.24284</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H51" s="6">
         <v>-1.5712299999999999</v>
       </c>
-      <c r="I51" s="1">
+      <c r="I51" s="6">
         <v>0.34949999999999998</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="6">
         <v>-0.4168</v>
       </c>
-      <c r="K51" s="1">
+      <c r="K51" s="6">
         <v>1.2729699999999999</v>
       </c>
-      <c r="L51" s="1">
+      <c r="L51" s="6">
         <v>-0.18598999999999999</v>
       </c>
-      <c r="M51" s="1">
+      <c r="M51" s="6">
         <v>-0.28965000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="6">
         <v>-1.45834</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="6">
         <v>1.22237</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" s="6">
         <v>0.23799000000000001</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="6">
         <v>-0.83570999999999995</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="6">
         <v>0.30564999999999998</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="6">
         <v>0.88924000000000003</v>
       </c>
-      <c r="H52" s="1">
+      <c r="H52" s="6">
         <v>-1.58524</v>
       </c>
-      <c r="I52" s="1">
+      <c r="I52" s="6">
         <v>0.46234999999999998</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="6">
         <v>-0.56679000000000002</v>
       </c>
-      <c r="K52" s="1">
+      <c r="K52" s="6">
         <v>2.00007</v>
       </c>
-      <c r="L52" s="1">
+      <c r="L52" s="6">
         <v>-7.8020000000000006E-2</v>
       </c>
-      <c r="M52" s="1">
+      <c r="M52" s="6">
         <v>2.818E-2</v>
       </c>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="6">
         <v>-1.19163</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="6">
         <v>0.92762</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="6">
         <v>1.0819000000000001</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="6">
         <v>-1.0128600000000001</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="6">
         <v>0.72331999999999996</v>
       </c>
-      <c r="G53" s="10">
+      <c r="G53" s="6">
         <v>1.0383</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H53" s="6">
         <v>-1.16934</v>
       </c>
-      <c r="I53" s="1">
+      <c r="I53" s="6">
         <v>0.44219999999999998</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="6">
         <v>-0.12898999999999999</v>
       </c>
-      <c r="K53" s="1">
+      <c r="K53" s="6">
         <v>1.0847199999999999</v>
       </c>
-      <c r="L53" s="1">
+      <c r="L53" s="6">
         <v>-9.4130000000000005E-2</v>
       </c>
-      <c r="M53" s="1">
+      <c r="M53" s="6">
         <v>-8.9819999999999997E-2</v>
       </c>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="6">
         <v>-1.4866299999999999</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="6">
         <v>1.30206</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="6">
         <v>0.12984999999999999</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="6">
         <v>-1.0191600000000001</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="6">
         <v>0.36193999999999998</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G54" s="6">
         <v>0.83679999999999999</v>
       </c>
-      <c r="H54" s="1">
+      <c r="H54" s="6">
         <v>-1.65351</v>
       </c>
-      <c r="I54" s="1">
+      <c r="I54" s="6">
         <v>0.40022000000000002</v>
       </c>
-      <c r="J54" s="1">
+      <c r="J54" s="6">
         <v>-0.71755999999999998</v>
       </c>
-      <c r="K54" s="1">
+      <c r="K54" s="6">
         <v>2.2714500000000002</v>
       </c>
-      <c r="L54" s="1">
+      <c r="L54" s="6">
         <v>-0.10839</v>
       </c>
-      <c r="M54" s="1">
+      <c r="M54" s="6">
         <v>4.2300000000000003E-3</v>
       </c>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="6">
         <v>-1.4370700000000001</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="6">
         <v>2.0295200000000002</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="6">
         <v>0.64453000000000005</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="6">
         <v>-0.60016000000000003</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="6">
         <v>0.59675</v>
       </c>
-      <c r="G55" s="10">
+      <c r="G55" s="6">
         <v>0.69079999999999997</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H55" s="6">
         <v>-1.4129499999999999</v>
       </c>
-      <c r="I55" s="1">
+      <c r="I55" s="6">
         <v>0.21609999999999999</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55" s="6">
         <v>-0.15584999999999999</v>
       </c>
-      <c r="K55" s="1">
+      <c r="K55" s="6">
         <v>1.07413</v>
       </c>
-      <c r="L55" s="1">
+      <c r="L55" s="6">
         <v>6.0600000000000003E-3</v>
       </c>
-      <c r="M55" s="1">
+      <c r="M55" s="6">
         <v>-7.0250000000000007E-2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
